--- a/results/nhanes__age-x-sex__routine-blood-tests/results.xlsx
+++ b/results/nhanes__age-x-sex__routine-blood-tests/results.xlsx
@@ -24,15 +24,15 @@
     <sheet name="select" sheetId="15" r:id="rId15"/>
     <sheet name="select_picks_summary" sheetId="16" r:id="rId16"/>
     <sheet name="pareto" sheetId="17" r:id="rId17"/>
-    <sheet name="external" sheetId="18" r:id="rId18"/>
-    <sheet name="shap_by_group" sheetId="19" r:id="rId19"/>
+    <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="403">
   <si>
     <t>Value</t>
   </si>
@@ -661,12 +661,18 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
@@ -676,12 +682,18 @@
     <t>0.723 ± 0.002</t>
   </si>
   <si>
+    <t>0.718 ± 0.001</t>
+  </si>
+  <si>
     <t>0.694 ± 0.007</t>
   </si>
   <si>
     <t>0.695 ± 0.018</t>
   </si>
   <si>
+    <t>0.719 ± 0.003</t>
+  </si>
+  <si>
     <t>0.724 ± 0.009</t>
   </si>
   <si>
@@ -691,6 +703,9 @@
     <t>0.755 ± 0.002</t>
   </si>
   <si>
+    <t>0.831 ± 0.003</t>
+  </si>
+  <si>
     <t>0.785 ± 0.003</t>
   </si>
   <si>
@@ -706,12 +721,18 @@
     <t>0.699 ± 0.002</t>
   </si>
   <si>
+    <t>0.691 ± 0.001</t>
+  </si>
+  <si>
     <t>0.660 ± 0.006</t>
   </si>
   <si>
     <t>0.610 ± 0.007</t>
   </si>
   <si>
+    <t>0.707 ± 0.003</t>
+  </si>
+  <si>
     <t>0.615 ± 0.007</t>
   </si>
   <si>
@@ -721,9 +742,15 @@
     <t>0.700 ± 0.005</t>
   </si>
   <si>
+    <t>0.679 ± 0.004</t>
+  </si>
+  <si>
     <t>0.614 ± 0.012</t>
   </si>
   <si>
+    <t>0.712 ± 0.004</t>
+  </si>
+  <si>
     <t>0.611 ± 0.011</t>
   </si>
   <si>
@@ -733,12 +760,18 @@
     <t>0.661 ± 0.004</t>
   </si>
   <si>
+    <t>0.649 ± 0.003</t>
+  </si>
+  <si>
     <t>0.605 ± 0.006</t>
   </si>
   <si>
     <t>0.475 ± 0.025</t>
   </si>
   <si>
+    <t>0.688 ± 0.003</t>
+  </si>
+  <si>
     <t>0.441 ± 0.012</t>
   </si>
   <si>
@@ -748,12 +781,18 @@
     <t>0.614 ± 0.008</t>
   </si>
   <si>
+    <t>0.439 ± 0.006</t>
+  </si>
+  <si>
     <t>0.564 ± 0.009</t>
   </si>
   <si>
     <t>0.511 ± 0.047</t>
   </si>
   <si>
+    <t>0.666 ± 0.007</t>
+  </si>
+  <si>
     <t>0.465 ± 0.030</t>
   </si>
   <si>
@@ -763,12 +802,18 @@
     <t>0.470 ± 0.003</t>
   </si>
   <si>
+    <t>0.461 ± 0.001</t>
+  </si>
+  <si>
     <t>0.423 ± 0.007</t>
   </si>
   <si>
     <t>0.366 ± 0.010</t>
   </si>
   <si>
+    <t>0.476 ± 0.003</t>
+  </si>
+  <si>
     <t>0.372 ± 0.010</t>
   </si>
   <si>
@@ -778,12 +823,18 @@
     <t>0.481 ± 0.006</t>
   </si>
   <si>
+    <t>0.490 ± 0.007</t>
+  </si>
+  <si>
     <t>0.493 ± 0.007</t>
   </si>
   <si>
     <t>0.372 ± 0.014</t>
   </si>
   <si>
+    <t>0.488 ± 0.006</t>
+  </si>
+  <si>
     <t>0.367 ± 0.014</t>
   </si>
   <si>
@@ -793,12 +844,18 @@
     <t>0.289 ± 0.007</t>
   </si>
   <si>
+    <t>0.260 ± 0.004</t>
+  </si>
+  <si>
     <t>0.171 ± 0.045</t>
   </si>
   <si>
     <t>0.068 ± 0.009</t>
   </si>
   <si>
+    <t>0.326 ± 0.015</t>
+  </si>
+  <si>
     <t>0.064 ± 0.010</t>
   </si>
   <si>
@@ -808,12 +865,18 @@
     <t>0.190 ± 0.008</t>
   </si>
   <si>
+    <t>0.209 ± 0.007</t>
+  </si>
+  <si>
     <t>0.222 ± 0.011</t>
   </si>
   <si>
     <t>0.067 ± 0.012</t>
   </si>
   <si>
+    <t>0.253 ± 0.016</t>
+  </si>
+  <si>
     <t>0.058 ± 0.009</t>
   </si>
   <si>
@@ -829,6 +892,9 @@
     <t>0.798 ± 0.036</t>
   </si>
   <si>
+    <t>0.425 ± 0.018</t>
+  </si>
+  <si>
     <t>0.782 ± 0.028</t>
   </si>
   <si>
@@ -838,12 +904,18 @@
     <t>0.537 ± 0.015</t>
   </si>
   <si>
+    <t>0.251 ± 0.015</t>
+  </si>
+  <si>
     <t>0.413 ± 0.017</t>
   </si>
   <si>
     <t>0.813 ± 0.051</t>
   </si>
   <si>
+    <t>0.475 ± 0.029</t>
+  </si>
+  <si>
     <t>0.818 ± 0.027</t>
   </si>
   <si>
@@ -853,12 +925,18 @@
     <t>0.300 ± 0.004</t>
   </si>
   <si>
+    <t>0.310 ± 0.016</t>
+  </si>
+  <si>
     <t>0.142 ± 0.038</t>
   </si>
   <si>
     <t>0.076 ± 0.035</t>
   </si>
   <si>
+    <t>0.389 ± 0.012</t>
+  </si>
+  <si>
     <t>0.051 ± 0.019</t>
   </si>
   <si>
@@ -868,12 +946,18 @@
     <t>0.267 ± 0.018</t>
   </si>
   <si>
+    <t>0.347 ± 0.027</t>
+  </si>
+  <si>
     <t>0.300 ± 0.017</t>
   </si>
   <si>
     <t>0.063 ± 0.023</t>
   </si>
   <si>
+    <t>0.316 ± 0.026</t>
+  </si>
+  <si>
     <t>0.046 ± 0.030</t>
   </si>
   <si>
@@ -892,12 +976,18 @@
     <t>0.335 ± 0.006</t>
   </si>
   <si>
+    <t>0.353 ± 0.006</t>
+  </si>
+  <si>
     <t>0.392 ± 0.014</t>
   </si>
   <si>
     <t>0.359 ± 0.033</t>
   </si>
   <si>
+    <t>0.322 ± 0.011</t>
+  </si>
+  <si>
     <t>0.384 ± 0.034</t>
   </si>
   <si>
@@ -907,12 +997,18 @@
     <t>0.406 ± 0.011</t>
   </si>
   <si>
+    <t>0.397 ± 0.020</t>
+  </si>
+  <si>
     <t>0.395 ± 0.011</t>
   </si>
   <si>
     <t>0.342 ± 0.015</t>
   </si>
   <si>
+    <t>0.363 ± 0.010</t>
+  </si>
+  <si>
     <t>0.354 ± 0.018</t>
   </si>
   <si>
@@ -922,12 +1018,18 @@
     <t>0.117 ± 0.009</t>
   </si>
   <si>
+    <t>0.086 ± 0.008</t>
+  </si>
+  <si>
     <t>0.081 ± 0.029</t>
   </si>
   <si>
     <t>0.066 ± 0.012</t>
   </si>
   <si>
+    <t>0.109 ± 0.006</t>
+  </si>
+  <si>
     <t>0.090 ± 0.004</t>
   </si>
   <si>
@@ -937,12 +1039,18 @@
     <t>0.068 ± 0.006</t>
   </si>
   <si>
+    <t>0.140 ± 0.005</t>
+  </si>
+  <si>
     <t>0.107 ± 0.008</t>
   </si>
   <si>
     <t>0.060 ± 0.027</t>
   </si>
   <si>
+    <t>0.091 ± 0.014</t>
+  </si>
+  <si>
     <t>0.074 ± 0.013</t>
   </si>
   <si>
@@ -970,12 +1078,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -985,12 +1099,18 @@
     <t>[-0.381, -0.249]</t>
   </si>
   <si>
+    <t>[-0.368, -0.235]</t>
+  </si>
+  <si>
     <t>[-0.551, -0.404]</t>
   </si>
   <si>
     <t>[-0.603, -0.426]</t>
   </si>
   <si>
+    <t>[-0.292, -0.168]</t>
+  </si>
+  <si>
     <t>[-0.613, -0.427]</t>
   </si>
   <si>
@@ -1000,12 +1120,18 @@
     <t>[-0.373, -0.227]</t>
   </si>
   <si>
+    <t>[-0.263, -0.133]</t>
+  </si>
+  <si>
     <t>[-0.338, -0.193]</t>
   </si>
   <si>
     <t>[-0.556, -0.388]</t>
   </si>
   <si>
+    <t>[-0.308, -0.183]</t>
+  </si>
+  <si>
     <t>[-0.575, -0.383]</t>
   </si>
   <si>
@@ -1015,12 +1141,18 @@
     <t>[-0.049, -0.021]</t>
   </si>
   <si>
+    <t>[-0.058, -0.030]</t>
+  </si>
+  <si>
     <t>[-0.100, -0.064]</t>
   </si>
   <si>
     <t>[-0.147, -0.109]</t>
   </si>
   <si>
+    <t>[-0.041, -0.017]</t>
+  </si>
+  <si>
     <t>[-0.144, -0.105]</t>
   </si>
   <si>
@@ -1030,12 +1162,18 @@
     <t>[-0.054, -0.024]</t>
   </si>
   <si>
+    <t>[-0.066, -0.036]</t>
+  </si>
+  <si>
     <t>[-0.052, -0.026]</t>
   </si>
   <si>
     <t>[-0.132, -0.092]</t>
   </si>
   <si>
+    <t>[-0.036, -0.011]</t>
+  </si>
+  <si>
     <t>[-0.140, -0.099]</t>
   </si>
   <si>
@@ -1060,31 +1198,31 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.767 ± 0.003</t>
+    <t>0.744 ± 0.020</t>
   </si>
   <si>
     <t>0.757 ± 0.003</t>
   </si>
   <si>
-    <t>0.711 ± 0.005</t>
+    <t>0.708 ± 0.008</t>
   </si>
   <si>
     <t>0.732 ± 0.003</t>
   </si>
   <si>
-    <t>0.623 ± 0.009</t>
+    <t>0.650 ± 0.010</t>
   </si>
   <si>
     <t>0.691 ± 0.014</t>
   </si>
   <si>
-    <t>0.425 ± 0.048</t>
+    <t>0.389 ± 0.064</t>
   </si>
   <si>
     <t>0.623 ± 0.010</t>
   </si>
   <si>
-    <t>0.356 ± 0.035</t>
+    <t>0.312 ± 0.053</t>
   </si>
   <si>
     <t>0.567 ± 0.000</t>
@@ -1097,6 +1235,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -3114,7 +3258,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3198,34 +3342,34 @@
         <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="F3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G3" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="H3" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="I3" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="J3" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="K3" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="L3" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3233,34 +3377,34 @@
         <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G4" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="H4" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="I4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="J4" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="K4" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="L4" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -3268,34 +3412,34 @@
         <v>209</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="G5" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="H5" t="s">
         <v>263</v>
       </c>
       <c r="I5" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="J5" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="K5" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="L5" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -3303,34 +3447,34 @@
         <v>210</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E6" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F6" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="G6" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="H6" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="I6" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="J6" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="K6" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="L6" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3338,253 +3482,393 @@
         <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G7" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I7" t="s">
+        <v>299</v>
+      </c>
+      <c r="J7" t="s">
+        <v>299</v>
+      </c>
+      <c r="K7" t="s">
+        <v>316</v>
+      </c>
+      <c r="L7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" t="s">
         <v>245</v>
       </c>
-      <c r="G7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H7" t="s">
-        <v>265</v>
-      </c>
-      <c r="I7" t="s">
-        <v>275</v>
-      </c>
-      <c r="J7" t="s">
-        <v>282</v>
-      </c>
-      <c r="K7" t="s">
-        <v>288</v>
-      </c>
-      <c r="L7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
-      </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>259</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="H8" t="s">
-        <v>143</v>
+        <v>286</v>
       </c>
       <c r="I8" t="s">
-        <v>151</v>
+        <v>300</v>
       </c>
       <c r="J8" t="s">
-        <v>151</v>
+        <v>300</v>
       </c>
       <c r="K8" t="s">
-        <v>159</v>
+        <v>317</v>
       </c>
       <c r="L8" t="s">
-        <v>166</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="F9" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="G9" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="H9" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="I9" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="J9" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="K9" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="L9" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C10" t="s">
-        <v>218</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>237</v>
+        <v>100</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>151</v>
       </c>
       <c r="J10" t="s">
-        <v>277</v>
+        <v>151</v>
       </c>
       <c r="K10" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="L10" t="s">
-        <v>300</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="G11" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="H11" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="I11" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="K11" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="L11" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E12" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F12" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G12" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="H12" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="I12" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="J12" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="K12" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="L12" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F13" t="s">
+        <v>263</v>
+      </c>
+      <c r="G13" t="s">
+        <v>277</v>
+      </c>
+      <c r="H13" t="s">
+        <v>290</v>
+      </c>
+      <c r="I13" t="s">
+        <v>304</v>
+      </c>
+      <c r="J13" t="s">
+        <v>304</v>
+      </c>
+      <c r="K13" t="s">
+        <v>321</v>
+      </c>
+      <c r="L13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H14" t="s">
+        <v>291</v>
+      </c>
+      <c r="I14" t="s">
+        <v>305</v>
+      </c>
+      <c r="J14" t="s">
+        <v>305</v>
+      </c>
+      <c r="K14" t="s">
+        <v>322</v>
+      </c>
+      <c r="L14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
         <v>211</v>
       </c>
-      <c r="C13" t="s">
-        <v>221</v>
-      </c>
-      <c r="D13" t="s">
-        <v>230</v>
-      </c>
-      <c r="E13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" t="s">
-        <v>250</v>
-      </c>
-      <c r="G13" t="s">
-        <v>260</v>
-      </c>
-      <c r="H13" t="s">
-        <v>270</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="C15" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F15" t="s">
+        <v>265</v>
+      </c>
+      <c r="G15" t="s">
+        <v>279</v>
+      </c>
+      <c r="H15" t="s">
+        <v>292</v>
+      </c>
+      <c r="I15" t="s">
+        <v>306</v>
+      </c>
+      <c r="J15" t="s">
+        <v>306</v>
+      </c>
+      <c r="K15" t="s">
+        <v>323</v>
+      </c>
+      <c r="L15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" t="s">
+        <v>252</v>
+      </c>
+      <c r="F16" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" t="s">
         <v>280</v>
       </c>
-      <c r="J13" t="s">
-        <v>283</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="H16" t="s">
         <v>293</v>
       </c>
-      <c r="L13" t="s">
-        <v>303</v>
+      <c r="I16" t="s">
+        <v>307</v>
+      </c>
+      <c r="J16" t="s">
+        <v>307</v>
+      </c>
+      <c r="K16" t="s">
+        <v>324</v>
+      </c>
+      <c r="L16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" t="s">
+        <v>253</v>
+      </c>
+      <c r="F17" t="s">
+        <v>267</v>
+      </c>
+      <c r="G17" t="s">
+        <v>281</v>
+      </c>
+      <c r="H17" t="s">
+        <v>294</v>
+      </c>
+      <c r="I17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J17" t="s">
+        <v>311</v>
+      </c>
+      <c r="K17" t="s">
+        <v>325</v>
+      </c>
+      <c r="L17" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3592,7 +3876,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3722,28 +4006,28 @@
         <v>209</v>
       </c>
       <c r="C5">
-        <v>0.657</v>
+        <v>0.752</v>
       </c>
       <c r="D5">
-        <v>0.335</v>
+        <v>0.384</v>
       </c>
       <c r="E5">
-        <v>0.612</v>
+        <v>0.699</v>
       </c>
       <c r="F5">
-        <v>0.263</v>
+        <v>0.323</v>
       </c>
       <c r="G5">
-        <v>0.518</v>
+        <v>0.442</v>
       </c>
       <c r="H5">
-        <v>0.313</v>
+        <v>0.229</v>
       </c>
       <c r="I5">
-        <v>0.581</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J5">
-        <v>0.243</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3751,28 +4035,28 @@
         <v>210</v>
       </c>
       <c r="C6">
-        <v>0.484</v>
+        <v>0.657</v>
       </c>
       <c r="D6">
-        <v>0.253</v>
+        <v>0.335</v>
       </c>
       <c r="E6">
-        <v>0.483</v>
+        <v>0.612</v>
       </c>
       <c r="F6">
-        <v>0.246</v>
+        <v>0.263</v>
       </c>
       <c r="G6">
-        <v>0.449</v>
+        <v>0.518</v>
       </c>
       <c r="H6">
-        <v>0.255</v>
+        <v>0.313</v>
       </c>
       <c r="I6">
-        <v>0.47</v>
+        <v>0.581</v>
       </c>
       <c r="J6">
-        <v>0.262</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3780,211 +4064,327 @@
         <v>211</v>
       </c>
       <c r="C7">
-        <v>0.444</v>
+        <v>0.484</v>
       </c>
       <c r="D7">
-        <v>0.207</v>
+        <v>0.253</v>
       </c>
       <c r="E7">
+        <v>0.483</v>
+      </c>
+      <c r="F7">
+        <v>0.246</v>
+      </c>
+      <c r="G7">
         <v>0.449</v>
       </c>
-      <c r="F7">
-        <v>0.198</v>
-      </c>
-      <c r="G7">
-        <v>0.425</v>
-      </c>
       <c r="H7">
-        <v>0.214</v>
+        <v>0.255</v>
       </c>
       <c r="I7">
+        <v>0.47</v>
+      </c>
+      <c r="J7">
+        <v>0.262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8">
+        <v>0.823</v>
+      </c>
+      <c r="D8">
+        <v>0.432</v>
+      </c>
+      <c r="E8">
+        <v>0.757</v>
+      </c>
+      <c r="F8">
+        <v>0.391</v>
+      </c>
+      <c r="G8">
         <v>0.434</v>
       </c>
-      <c r="J7">
-        <v>0.216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8">
-        <v>0.839</v>
-      </c>
-      <c r="D8">
-        <v>0.459</v>
-      </c>
-      <c r="E8">
-        <v>0.85</v>
-      </c>
-      <c r="F8">
-        <v>0.495</v>
-      </c>
-      <c r="G8">
-        <v>0.272</v>
-      </c>
       <c r="H8">
-        <v>0.082</v>
+        <v>0.219</v>
       </c>
       <c r="I8">
-        <v>0.396</v>
+        <v>0.549</v>
       </c>
       <c r="J8">
-        <v>0.08699999999999999</v>
+        <v>0.215</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C9">
-        <v>0.772</v>
+        <v>0.444</v>
       </c>
       <c r="D9">
-        <v>0.394</v>
+        <v>0.207</v>
       </c>
       <c r="E9">
-        <v>0.803</v>
+        <v>0.449</v>
       </c>
       <c r="F9">
-        <v>0.423</v>
+        <v>0.198</v>
       </c>
       <c r="G9">
-        <v>0.303</v>
+        <v>0.425</v>
       </c>
       <c r="H9">
-        <v>0.104</v>
+        <v>0.214</v>
       </c>
       <c r="I9">
-        <v>0.469</v>
+        <v>0.434</v>
       </c>
       <c r="J9">
-        <v>0.134</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C10">
-        <v>0.675</v>
+        <v>0.839</v>
       </c>
       <c r="D10">
-        <v>0.244</v>
+        <v>0.459</v>
       </c>
       <c r="E10">
-        <v>0.6919999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F10">
-        <v>0.263</v>
+        <v>0.495</v>
       </c>
       <c r="G10">
-        <v>0.429</v>
+        <v>0.272</v>
       </c>
       <c r="H10">
-        <v>0.206</v>
+        <v>0.082</v>
       </c>
       <c r="I10">
-        <v>0.533</v>
+        <v>0.396</v>
       </c>
       <c r="J10">
-        <v>0.188</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11">
-        <v>0.661</v>
+        <v>0.772</v>
       </c>
       <c r="D11">
-        <v>0.225</v>
+        <v>0.394</v>
       </c>
       <c r="E11">
-        <v>0.638</v>
+        <v>0.803</v>
       </c>
       <c r="F11">
-        <v>0.23</v>
+        <v>0.423</v>
       </c>
       <c r="G11">
-        <v>0.361</v>
+        <v>0.303</v>
       </c>
       <c r="H11">
-        <v>0.15</v>
+        <v>0.104</v>
       </c>
       <c r="I11">
-        <v>0.437</v>
+        <v>0.469</v>
       </c>
       <c r="J11">
-        <v>0.127</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C12">
-        <v>0.508</v>
+        <v>0.675</v>
       </c>
       <c r="D12">
-        <v>0.287</v>
+        <v>0.244</v>
       </c>
       <c r="E12">
-        <v>0.513</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F12">
-        <v>0.274</v>
+        <v>0.263</v>
       </c>
       <c r="G12">
-        <v>0.512</v>
+        <v>0.429</v>
       </c>
       <c r="H12">
-        <v>0.283</v>
+        <v>0.206</v>
       </c>
       <c r="I12">
-        <v>0.511</v>
+        <v>0.533</v>
       </c>
       <c r="J12">
-        <v>0.284</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13">
+        <v>0.524</v>
+      </c>
+      <c r="D13">
+        <v>0.132</v>
+      </c>
+      <c r="E13">
+        <v>0.537</v>
+      </c>
+      <c r="F13">
+        <v>0.143</v>
+      </c>
+      <c r="G13">
+        <v>0.195</v>
+      </c>
+      <c r="H13">
+        <v>0.056</v>
+      </c>
+      <c r="I13">
+        <v>0.329</v>
+      </c>
+      <c r="J13">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14">
+        <v>0.661</v>
+      </c>
+      <c r="D14">
+        <v>0.225</v>
+      </c>
+      <c r="E14">
+        <v>0.638</v>
+      </c>
+      <c r="F14">
+        <v>0.23</v>
+      </c>
+      <c r="G14">
+        <v>0.361</v>
+      </c>
+      <c r="H14">
+        <v>0.15</v>
+      </c>
+      <c r="I14">
+        <v>0.437</v>
+      </c>
+      <c r="J14">
+        <v>0.127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" t="s">
         <v>211</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.508</v>
+      </c>
+      <c r="D15">
+        <v>0.287</v>
+      </c>
+      <c r="E15">
+        <v>0.513</v>
+      </c>
+      <c r="F15">
+        <v>0.274</v>
+      </c>
+      <c r="G15">
+        <v>0.512</v>
+      </c>
+      <c r="H15">
+        <v>0.283</v>
+      </c>
+      <c r="I15">
+        <v>0.511</v>
+      </c>
+      <c r="J15">
+        <v>0.284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16">
+        <v>0.744</v>
+      </c>
+      <c r="D16">
+        <v>0.323</v>
+      </c>
+      <c r="E16">
+        <v>0.755</v>
+      </c>
+      <c r="F16">
+        <v>0.337</v>
+      </c>
+      <c r="G16">
+        <v>0.442</v>
+      </c>
+      <c r="H16">
+        <v>0.217</v>
+      </c>
+      <c r="I16">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="J16">
+        <v>0.194</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17">
         <v>0.466</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.235</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.462</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.232</v>
       </c>
-      <c r="G13">
+      <c r="G17">
         <v>0.466</v>
       </c>
-      <c r="H13">
+      <c r="H17">
         <v>0.249</v>
       </c>
-      <c r="I13">
+      <c r="I17">
         <v>0.469</v>
       </c>
-      <c r="J13">
+      <c r="J17">
         <v>0.243</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3992,7 +4392,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4003,22 +4403,22 @@
         <v>205</v>
       </c>
       <c r="D1" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="E1" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="F1" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="G1" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="H1" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="I1" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4029,13 +4429,13 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="D2">
         <v>-0.073</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4044,7 +4444,7 @@
         <v>-0.007</v>
       </c>
       <c r="H2" t="s">
-        <v>325</v>
+        <v>367</v>
       </c>
       <c r="I2">
         <v>0.07000000000000001</v>
@@ -4058,13 +4458,13 @@
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="D3">
         <v>-0.313</v>
       </c>
       <c r="E3" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -4073,7 +4473,7 @@
         <v>-0.035</v>
       </c>
       <c r="H3" t="s">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4087,22 +4487,22 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="D4">
-        <v>-0.48</v>
+        <v>-0.301</v>
       </c>
       <c r="E4" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>-0.082</v>
+        <v>-0.044</v>
       </c>
       <c r="H4" t="s">
-        <v>327</v>
+        <v>369</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4116,22 +4516,22 @@
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="D5">
-        <v>-0.521</v>
+        <v>-0.48</v>
       </c>
       <c r="E5" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>-0.128</v>
+        <v>-0.082</v>
       </c>
       <c r="H5" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4145,22 +4545,22 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="D6">
-        <v>-0.531</v>
+        <v>-0.521</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>-0.125</v>
+        <v>-0.128</v>
       </c>
       <c r="H6" t="s">
-        <v>329</v>
+        <v>371</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4171,28 +4571,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="D7">
-        <v>-0.083</v>
+        <v>-0.227</v>
       </c>
       <c r="E7" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="F7">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-0.016</v>
+        <v>-0.028</v>
       </c>
       <c r="H7" t="s">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="I7">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -4200,25 +4600,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="D8">
-        <v>-0.303</v>
+        <v>-0.531</v>
       </c>
       <c r="E8" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>-0.039</v>
+        <v>-0.125</v>
       </c>
       <c r="H8" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4232,25 +4632,25 @@
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="D9">
-        <v>-0.262</v>
+        <v>-0.083</v>
       </c>
       <c r="E9" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G9">
-        <v>-0.04</v>
+        <v>-0.016</v>
       </c>
       <c r="H9" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4261,22 +4661,22 @@
         <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="D10">
-        <v>-0.478</v>
+        <v>-0.303</v>
       </c>
       <c r="E10" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>-0.112</v>
+        <v>-0.039</v>
       </c>
       <c r="H10" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4290,24 +4690,140 @@
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="D11">
+        <v>-0.198</v>
+      </c>
+      <c r="E11" t="s">
+        <v>362</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>-0.051</v>
+      </c>
+      <c r="H11" t="s">
+        <v>376</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>349</v>
+      </c>
+      <c r="D12">
+        <v>-0.262</v>
+      </c>
+      <c r="E12" t="s">
+        <v>363</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>-0.04</v>
+      </c>
+      <c r="H12" t="s">
+        <v>377</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D13">
+        <v>-0.478</v>
+      </c>
+      <c r="E13" t="s">
+        <v>364</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>-0.112</v>
+      </c>
+      <c r="H13" t="s">
+        <v>378</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>351</v>
+      </c>
+      <c r="D14">
+        <v>-0.246</v>
+      </c>
+      <c r="E14" t="s">
+        <v>365</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>-0.024</v>
+      </c>
+      <c r="H14" t="s">
+        <v>379</v>
+      </c>
+      <c r="I14">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>352</v>
+      </c>
+      <c r="D15">
         <v>-0.486</v>
       </c>
-      <c r="E11" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="E15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>-0.119</v>
       </c>
-      <c r="H11" t="s">
-        <v>334</v>
-      </c>
-      <c r="I11">
+      <c r="H15" t="s">
+        <v>380</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
     </row>
@@ -4323,13 +4839,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="C1" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="D1" t="s">
-        <v>337</v>
+        <v>383</v>
       </c>
       <c r="E1" t="s">
         <v>187</v>
@@ -4338,10 +4854,10 @@
         <v>205</v>
       </c>
       <c r="G1" t="s">
-        <v>338</v>
+        <v>384</v>
       </c>
       <c r="H1" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4355,13 +4871,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E2" t="s">
         <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="G2">
         <v>0.708</v>
@@ -4381,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E3" t="s">
         <v>79</v>
@@ -4407,13 +4923,13 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="G4">
         <v>0.719</v>
@@ -4433,7 +4949,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E5" t="s">
         <v>73</v>
@@ -4459,19 +4975,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="G6">
-        <v>0.714</v>
+        <v>0.709</v>
       </c>
       <c r="H6">
-        <v>0.52</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4485,7 +5001,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E7" t="s">
         <v>73</v>
@@ -4511,19 +5027,19 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E8" t="s">
         <v>79</v>
       </c>
       <c r="F8" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="G8">
-        <v>0.702</v>
+        <v>0.704</v>
       </c>
       <c r="H8">
-        <v>0.312</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4537,7 +5053,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E9" t="s">
         <v>73</v>
@@ -4563,19 +5079,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="G10">
-        <v>0.726</v>
+        <v>0.714</v>
       </c>
       <c r="H10">
-        <v>0.5</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4589,7 +5105,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E11" t="s">
         <v>73</v>
@@ -4615,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E12" t="s">
         <v>79</v>
@@ -4641,7 +5157,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E13" t="s">
         <v>73</v>
@@ -4667,19 +5183,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="G14">
-        <v>0.709</v>
+        <v>0.701</v>
       </c>
       <c r="H14">
-        <v>0.485</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4693,7 +5209,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E15" t="s">
         <v>73</v>
@@ -4719,13 +5235,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="G16">
         <v>0.709</v>
@@ -4745,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E17" t="s">
         <v>73</v>
@@ -4771,13 +5287,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E18" t="s">
         <v>79</v>
       </c>
       <c r="F18" t="s">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="G18">
         <v>0.708</v>
@@ -4797,7 +5313,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E19" t="s">
         <v>79</v>
@@ -4823,13 +5339,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="G20">
         <v>0.711</v>
@@ -4849,7 +5365,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="E21" t="s">
         <v>79</v>
@@ -4876,7 +5392,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>383</v>
       </c>
       <c r="B1" t="s">
         <v>67</v>
@@ -4899,48 +5415,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>388</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
       <c r="E2" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="F2" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="G2" t="s">
-        <v>350</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="B3" t="s">
-        <v>343</v>
+        <v>389</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>391</v>
       </c>
       <c r="D3" t="s">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="E3" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="F3" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="G3" t="s">
-        <v>351</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -4950,7 +5466,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4961,7 +5477,7 @@
         <v>205</v>
       </c>
       <c r="D1" t="s">
-        <v>352</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4969,13 +5485,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>351</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4986,10 +5502,10 @@
         <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5000,10 +5516,10 @@
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -5014,10 +5530,38 @@
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
         <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5027,7 +5571,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5044,7 +5588,7 @@
         <v>125</v>
       </c>
       <c r="E1" t="s">
-        <v>353</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5097,13 +5641,13 @@
         <v>209</v>
       </c>
       <c r="C5">
-        <v>0.66</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="D5">
-        <v>0.144</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5111,13 +5655,13 @@
         <v>210</v>
       </c>
       <c r="C6">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="D6">
-        <v>0.076</v>
+        <v>0.144</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5125,55 +5669,55 @@
         <v>211</v>
       </c>
       <c r="C7">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="D7">
-        <v>0.052</v>
+        <v>0.076</v>
       </c>
       <c r="E7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>79</v>
-      </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C8">
-        <v>0.737</v>
+        <v>0.707</v>
       </c>
       <c r="D8">
-        <v>0.578</v>
+        <v>0.389</v>
       </c>
       <c r="E8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C9">
-        <v>0.724</v>
+        <v>0.615</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.052</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C10">
-        <v>0.7</v>
+        <v>0.737</v>
       </c>
       <c r="D10">
-        <v>0.267</v>
+        <v>0.578</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -5181,50 +5725,106 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C11">
-        <v>0.7</v>
+        <v>0.724</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C12">
-        <v>0.614</v>
+        <v>0.7</v>
       </c>
       <c r="D12">
-        <v>0.063</v>
+        <v>0.267</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C13">
+        <v>0.679</v>
+      </c>
+      <c r="D13">
+        <v>0.347</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14">
+        <v>0.7</v>
+      </c>
+      <c r="D14">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>211</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.614</v>
+      </c>
+      <c r="D15">
+        <v>0.063</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16">
+        <v>0.712</v>
+      </c>
+      <c r="D16">
+        <v>0.316</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17">
         <v>0.611</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.053</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5232,443 +5832,364 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:6">
       <c r="B1" t="s">
-        <v>187</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J1" t="s">
-        <v>167</v>
-      </c>
-      <c r="K1" t="s">
-        <v>172</v>
-      </c>
-      <c r="L1" t="s">
-        <v>177</v>
-      </c>
-      <c r="M1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
-        <v>206</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>0.5375000238418579</v>
+      </c>
+      <c r="C2">
+        <v>0.539900004863739</v>
       </c>
       <c r="D2">
-        <v>0.784</v>
+        <v>0.4639999866485596</v>
       </c>
       <c r="E2">
-        <v>0.749</v>
+        <v>0.4964999854564667</v>
       </c>
       <c r="F2">
-        <v>0.696</v>
-      </c>
-      <c r="G2">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="H2">
-        <v>0.508</v>
-      </c>
-      <c r="I2">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="J2">
-        <v>0.891</v>
-      </c>
-      <c r="K2">
-        <v>0.853</v>
-      </c>
-      <c r="L2">
-        <v>0.383</v>
-      </c>
-      <c r="M2">
-        <v>0.415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>311</v>
+        <v>0.5005999803543091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>0.5527999997138977</v>
+      </c>
+      <c r="C3">
+        <v>0.5473999977111816</v>
       </c>
       <c r="D3">
-        <v>0.744</v>
+        <v>0.3409000039100647</v>
       </c>
       <c r="E3">
-        <v>0.708</v>
+        <v>0.3084999918937683</v>
       </c>
       <c r="F3">
-        <v>0.654</v>
-      </c>
-      <c r="G3">
-        <v>0.757</v>
-      </c>
-      <c r="H3">
-        <v>0.206</v>
-      </c>
-      <c r="I3">
-        <v>0.206</v>
-      </c>
-      <c r="J3">
-        <v>0.737</v>
-      </c>
-      <c r="K3">
-        <v>0.699</v>
-      </c>
-      <c r="L3">
-        <v>0.553</v>
-      </c>
-      <c r="M3">
-        <v>0.531</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>312</v>
+        <v>0.4066999852657318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4">
+        <v>0.2804000079631805</v>
+      </c>
+      <c r="C4">
+        <v>0.2565000057220459</v>
       </c>
       <c r="D4">
-        <v>0.707</v>
+        <v>0.2137999981641769</v>
       </c>
       <c r="E4">
-        <v>0.675</v>
+        <v>0.2353000044822693</v>
       </c>
       <c r="F4">
-        <v>0.628</v>
-      </c>
-      <c r="G4">
-        <v>0.701</v>
-      </c>
-      <c r="H4">
-        <v>0.108</v>
-      </c>
-      <c r="I4">
-        <v>0.108</v>
-      </c>
-      <c r="J4">
-        <v>0.669</v>
-      </c>
-      <c r="K4">
-        <v>0.652</v>
-      </c>
-      <c r="L4">
-        <v>0.58</v>
-      </c>
-      <c r="M4">
-        <v>0.5620000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>313</v>
+        <v>0.2398000061511993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5">
+        <v>0.2858000099658966</v>
+      </c>
+      <c r="C5">
+        <v>0.2533999979496002</v>
       </c>
       <c r="D5">
-        <v>0.77</v>
+        <v>0.2314999997615814</v>
       </c>
       <c r="E5">
-        <v>0.64</v>
+        <v>0.2022999972105026</v>
       </c>
       <c r="F5">
-        <v>0.447</v>
-      </c>
-      <c r="H5">
-        <v>0.104</v>
-      </c>
-      <c r="I5">
-        <v>0.104</v>
-      </c>
-      <c r="J5">
-        <v>0.466</v>
-      </c>
-      <c r="K5">
-        <v>0.391</v>
-      </c>
-      <c r="L5">
-        <v>0.495</v>
-      </c>
-      <c r="M5">
-        <v>0.462</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>314</v>
+        <v>0.2364999949932098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6">
+        <v>0.1861999928951263</v>
+      </c>
+      <c r="C6">
+        <v>0.2318000048398972</v>
       </c>
       <c r="D6">
-        <v>0.774</v>
+        <v>0.1519999951124191</v>
       </c>
       <c r="E6">
-        <v>0.641</v>
+        <v>0.1705999970436096</v>
       </c>
       <c r="F6">
-        <v>0.444</v>
-      </c>
-      <c r="H6">
-        <v>0.097</v>
-      </c>
-      <c r="I6">
-        <v>0.097</v>
-      </c>
-      <c r="J6">
-        <v>0.44</v>
-      </c>
-      <c r="K6">
-        <v>0.409</v>
-      </c>
-      <c r="L6">
-        <v>0.505</v>
-      </c>
-      <c r="M6">
-        <v>0.438</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>206</v>
+        <v>0.1782000064849854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7">
+        <v>0.1763000041246414</v>
+      </c>
+      <c r="C7">
+        <v>0.1917999982833862</v>
       </c>
       <c r="D7">
-        <v>0.791</v>
+        <v>0.1473000049591064</v>
       </c>
       <c r="E7">
-        <v>0.74</v>
+        <v>0.1791000068187714</v>
       </c>
       <c r="F7">
-        <v>0.666</v>
-      </c>
-      <c r="G7">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="H7">
-        <v>0.488</v>
-      </c>
-      <c r="I7">
-        <v>0.488</v>
-      </c>
-      <c r="J7">
-        <v>0.857</v>
-      </c>
-      <c r="K7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L7">
-        <v>0.388</v>
-      </c>
-      <c r="M7">
-        <v>0.369</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>311</v>
+        <v>0.1701000034809113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8">
+        <v>0.127700001001358</v>
+      </c>
+      <c r="C8">
+        <v>0.1167000010609627</v>
       </c>
       <c r="D8">
-        <v>0.75</v>
+        <v>0.1289999932050705</v>
       </c>
       <c r="E8">
-        <v>0.699</v>
+        <v>0.1234999969601631</v>
       </c>
       <c r="F8">
-        <v>0.622</v>
-      </c>
-      <c r="G8">
-        <v>0.758</v>
-      </c>
-      <c r="H8">
-        <v>0.195</v>
-      </c>
-      <c r="I8">
-        <v>0.195</v>
-      </c>
-      <c r="J8">
-        <v>0.703</v>
-      </c>
-      <c r="K8">
-        <v>0.627</v>
-      </c>
-      <c r="L8">
-        <v>0.58</v>
-      </c>
-      <c r="M8">
-        <v>0.508</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>312</v>
+        <v>0.1248999983072281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9">
+        <v>0.1036000028252602</v>
+      </c>
+      <c r="C9">
+        <v>0.1440999954938889</v>
       </c>
       <c r="D9">
-        <v>0.788</v>
+        <v>0.1046999990940094</v>
       </c>
       <c r="E9">
-        <v>0.695</v>
+        <v>0.1479000002145767</v>
       </c>
       <c r="F9">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="G9">
-        <v>0.72</v>
-      </c>
-      <c r="H9">
-        <v>0.182</v>
-      </c>
-      <c r="I9">
-        <v>0.182</v>
-      </c>
-      <c r="J9">
-        <v>0.62</v>
-      </c>
-      <c r="K9">
-        <v>0.591</v>
-      </c>
-      <c r="L9">
-        <v>0.5</v>
-      </c>
-      <c r="M9">
-        <v>0.438</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>313</v>
+        <v>0.124600000679493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10">
+        <v>0.09650000184774399</v>
+      </c>
+      <c r="C10">
+        <v>0.08349999785423279</v>
       </c>
       <c r="D10">
-        <v>0.677</v>
+        <v>0.152099996805191</v>
       </c>
       <c r="E10">
-        <v>0.646</v>
+        <v>0.1253000050783157</v>
       </c>
       <c r="F10">
-        <v>0.6</v>
-      </c>
-      <c r="H10">
-        <v>0.136</v>
-      </c>
-      <c r="I10">
-        <v>0.136</v>
-      </c>
-      <c r="J10">
-        <v>0.62</v>
-      </c>
-      <c r="K10">
-        <v>0.523</v>
-      </c>
-      <c r="L10">
-        <v>0.66</v>
-      </c>
-      <c r="M10">
-        <v>0.638</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>314</v>
+        <v>0.1216999962925911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11">
+        <v>0.1083000004291534</v>
+      </c>
+      <c r="C11">
+        <v>0.1099999994039536</v>
       </c>
       <c r="D11">
-        <v>0.618</v>
+        <v>0.1022000014781952</v>
       </c>
       <c r="E11">
-        <v>0.63</v>
+        <v>0.1275999993085861</v>
       </c>
       <c r="F11">
-        <v>0.648</v>
-      </c>
-      <c r="H11">
-        <v>0.154</v>
-      </c>
-      <c r="I11">
-        <v>0.154</v>
-      </c>
-      <c r="J11">
-        <v>0.707</v>
-      </c>
-      <c r="K11">
-        <v>0.5590000000000001</v>
-      </c>
-      <c r="L11">
-        <v>0.713</v>
-      </c>
-      <c r="M11">
-        <v>0.623</v>
+        <v>0.1123000010848045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12">
+        <v>0.08969999849796295</v>
+      </c>
+      <c r="C12">
+        <v>0.1006999984383583</v>
+      </c>
+      <c r="D12">
+        <v>0.08799999952316284</v>
+      </c>
+      <c r="E12">
+        <v>0.08829999715089798</v>
+      </c>
+      <c r="F12">
+        <v>0.09070000052452087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <v>0.06750000268220901</v>
+      </c>
+      <c r="C13">
+        <v>0.1080999970436096</v>
+      </c>
+      <c r="D13">
+        <v>0.06419999897480011</v>
+      </c>
+      <c r="E13">
+        <v>0.1228000000119209</v>
+      </c>
+      <c r="F13">
+        <v>0.09030000120401382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0.08179999887943268</v>
+      </c>
+      <c r="C14">
+        <v>0.09780000150203705</v>
+      </c>
+      <c r="D14">
+        <v>0.0601000003516674</v>
+      </c>
+      <c r="E14">
+        <v>0.07360000163316727</v>
+      </c>
+      <c r="F14">
+        <v>0.07490000128746033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15">
+        <v>0.06060000136494637</v>
+      </c>
+      <c r="C15">
+        <v>0.07339999824762344</v>
+      </c>
+      <c r="D15">
+        <v>0.05860000103712082</v>
+      </c>
+      <c r="E15">
+        <v>0.07299999892711639</v>
+      </c>
+      <c r="F15">
+        <v>0.06599999964237213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16">
+        <v>0.05330000072717667</v>
+      </c>
+      <c r="C16">
+        <v>0.05209999904036522</v>
+      </c>
+      <c r="D16">
+        <v>0.05209999904036522</v>
+      </c>
+      <c r="E16">
+        <v>0.06230000033974648</v>
+      </c>
+      <c r="F16">
+        <v>0.05539999902248383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17">
+        <v>0.02930000051856041</v>
+      </c>
+      <c r="C17">
+        <v>0.02710000053048134</v>
+      </c>
+      <c r="D17">
+        <v>0.02820000052452087</v>
+      </c>
+      <c r="E17">
+        <v>0.02940000034868717</v>
+      </c>
+      <c r="F17">
+        <v>0.02859999984502792</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5678,364 +6199,91 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>3.24</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>3.36</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>2.92</v>
+      </c>
+      <c r="D4">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2">
-        <v>0.5375000238418579</v>
-      </c>
-      <c r="C2">
-        <v>0.539900004863739</v>
-      </c>
-      <c r="D2">
-        <v>0.4639999866485596</v>
-      </c>
-      <c r="E2">
-        <v>0.4964999854564667</v>
-      </c>
-      <c r="F2">
-        <v>0.5005999803543091</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3">
-        <v>0.5527999997138977</v>
-      </c>
-      <c r="C3">
-        <v>0.5473999977111816</v>
-      </c>
-      <c r="D3">
-        <v>0.3409000039100647</v>
-      </c>
-      <c r="E3">
-        <v>0.3084999918937683</v>
-      </c>
-      <c r="F3">
-        <v>0.4066999852657318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4">
-        <v>0.2804000079631805</v>
-      </c>
-      <c r="C4">
-        <v>0.2565000057220459</v>
-      </c>
-      <c r="D4">
-        <v>0.2137999981641769</v>
-      </c>
-      <c r="E4">
-        <v>0.2353000044822693</v>
-      </c>
-      <c r="F4">
-        <v>0.2398000061511993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>58</v>
-      </c>
       <c r="B5">
-        <v>0.2858000099658966</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>0.2533999979496002</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>0.2314999997615814</v>
-      </c>
-      <c r="E5">
-        <v>0.2022999972105026</v>
-      </c>
-      <c r="F5">
-        <v>0.2364999949932098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>0.1861999928951263</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>0.2318000048398972</v>
+        <v>3.13</v>
       </c>
       <c r="D6">
-        <v>0.1519999951124191</v>
-      </c>
-      <c r="E6">
-        <v>0.1705999970436096</v>
-      </c>
-      <c r="F6">
-        <v>0.1782000064849854</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7">
-        <v>0.1763000041246414</v>
-      </c>
-      <c r="C7">
-        <v>0.1917999982833862</v>
-      </c>
-      <c r="D7">
-        <v>0.1473000049591064</v>
-      </c>
-      <c r="E7">
-        <v>0.1791000068187714</v>
-      </c>
-      <c r="F7">
-        <v>0.1701000034809113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8">
-        <v>0.127700001001358</v>
-      </c>
-      <c r="C8">
-        <v>0.1167000010609627</v>
-      </c>
-      <c r="D8">
-        <v>0.1289999932050705</v>
-      </c>
-      <c r="E8">
-        <v>0.1234999969601631</v>
-      </c>
-      <c r="F8">
-        <v>0.1248999983072281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9">
-        <v>0.1036000028252602</v>
-      </c>
-      <c r="C9">
-        <v>0.1440999954938889</v>
-      </c>
-      <c r="D9">
-        <v>0.1046999990940094</v>
-      </c>
-      <c r="E9">
-        <v>0.1479000002145767</v>
-      </c>
-      <c r="F9">
-        <v>0.124600000679493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>0.09650000184774399</v>
-      </c>
-      <c r="C10">
-        <v>0.08349999785423279</v>
-      </c>
-      <c r="D10">
-        <v>0.152099996805191</v>
-      </c>
-      <c r="E10">
-        <v>0.1253000050783157</v>
-      </c>
-      <c r="F10">
-        <v>0.1216999962925911</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11">
-        <v>0.1083000004291534</v>
-      </c>
-      <c r="C11">
-        <v>0.1099999994039536</v>
-      </c>
-      <c r="D11">
-        <v>0.1022000014781952</v>
-      </c>
-      <c r="E11">
-        <v>0.1275999993085861</v>
-      </c>
-      <c r="F11">
-        <v>0.1123000010848045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12">
-        <v>0.08969999849796295</v>
-      </c>
-      <c r="C12">
-        <v>0.1006999984383583</v>
-      </c>
-      <c r="D12">
-        <v>0.08799999952316284</v>
-      </c>
-      <c r="E12">
-        <v>0.08829999715089798</v>
-      </c>
-      <c r="F12">
-        <v>0.09070000052452087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13">
-        <v>0.06750000268220901</v>
-      </c>
-      <c r="C13">
-        <v>0.1080999970436096</v>
-      </c>
-      <c r="D13">
-        <v>0.06419999897480011</v>
-      </c>
-      <c r="E13">
-        <v>0.1228000000119209</v>
-      </c>
-      <c r="F13">
-        <v>0.09030000120401382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14">
-        <v>0.08179999887943268</v>
-      </c>
-      <c r="C14">
-        <v>0.09780000150203705</v>
-      </c>
-      <c r="D14">
-        <v>0.0601000003516674</v>
-      </c>
-      <c r="E14">
-        <v>0.07360000163316727</v>
-      </c>
-      <c r="F14">
-        <v>0.07490000128746033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15">
-        <v>0.06060000136494637</v>
-      </c>
-      <c r="C15">
-        <v>0.07339999824762344</v>
-      </c>
-      <c r="D15">
-        <v>0.05860000103712082</v>
-      </c>
-      <c r="E15">
-        <v>0.07299999892711639</v>
-      </c>
-      <c r="F15">
-        <v>0.06599999964237213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16">
-        <v>0.05330000072717667</v>
-      </c>
-      <c r="C16">
-        <v>0.05209999904036522</v>
-      </c>
-      <c r="D16">
-        <v>0.05209999904036522</v>
-      </c>
-      <c r="E16">
-        <v>0.06230000033974648</v>
-      </c>
-      <c r="F16">
-        <v>0.05539999902248383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17">
-        <v>0.02930000051856041</v>
-      </c>
-      <c r="C17">
-        <v>0.02710000053048134</v>
-      </c>
-      <c r="D17">
-        <v>0.02820000052452087</v>
-      </c>
-      <c r="E17">
-        <v>0.02940000034868717</v>
-      </c>
-      <c r="F17">
-        <v>0.02859999984502792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
